--- a/software/python_processing/dataset_stats/cLASIr No Acc AP Stats.xlsx
+++ b/software/python_processing/dataset_stats/cLASIr No Acc AP Stats.xlsx
@@ -436,12 +436,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Class 1.0</t>
+          <t>Class 1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Class 0.0</t>
+          <t>Class 0</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>214</v>
+        <v>754</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>322</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="4">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>236</v>
+        <v>736</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>228</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>772</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>180</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>234</v>
+        <v>818</v>
       </c>
       <c r="C8" t="inlineStr"/>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>264</v>
+        <v>734</v>
       </c>
       <c r="C10" t="inlineStr"/>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>384</v>
+        <v>882</v>
       </c>
     </row>
     <row r="12">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>262</v>
+        <v>786</v>
       </c>
       <c r="C12" t="inlineStr"/>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>230</v>
+        <v>712</v>
       </c>
     </row>
     <row r="14">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>222</v>
+        <v>934</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>242</v>
+        <v>894</v>
       </c>
     </row>
     <row r="16">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>290</v>
+        <v>739</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>226</v>
+        <v>730</v>
       </c>
     </row>
     <row r="18">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>232</v>
+        <v>766</v>
       </c>
       <c r="C18" t="inlineStr"/>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>214</v>
+        <v>812</v>
       </c>
     </row>
     <row r="20">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>246</v>
+        <v>738</v>
       </c>
       <c r="C20" t="inlineStr"/>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>224</v>
+        <v>660</v>
       </c>
     </row>
     <row r="22">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>254</v>
+        <v>726</v>
       </c>
       <c r="C22" t="inlineStr"/>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>212</v>
+        <v>818</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>208</v>
+        <v>744</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>232</v>
+        <v>794</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>232</v>
+        <v>804</v>
       </c>
     </row>
     <row r="27">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>246</v>
+        <v>702</v>
       </c>
       <c r="C27" t="inlineStr"/>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>216</v>
+        <v>730</v>
       </c>
     </row>
     <row r="29">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>266</v>
+        <v>656</v>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>228</v>
+        <v>852</v>
       </c>
     </row>
     <row r="31">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>246</v>
+        <v>782</v>
       </c>
       <c r="C31" t="inlineStr"/>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>242</v>
+        <v>794</v>
       </c>
     </row>
     <row r="33">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>230</v>
+        <v>866</v>
       </c>
       <c r="C33" t="inlineStr"/>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>254</v>
+        <v>746</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>246</v>
+        <v>666</v>
       </c>
       <c r="C35" t="inlineStr"/>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>230</v>
+        <v>806</v>
       </c>
     </row>
     <row r="37">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>254</v>
+        <v>760</v>
       </c>
       <c r="C37" t="inlineStr"/>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>242</v>
+        <v>704</v>
       </c>
     </row>
     <row r="39">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>260</v>
+        <v>746</v>
       </c>
       <c r="C39" t="inlineStr"/>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>234</v>
+        <v>718</v>
       </c>
     </row>
     <row r="41">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>230</v>
+        <v>748</v>
       </c>
       <c r="C41" t="inlineStr"/>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>210</v>
+        <v>792</v>
       </c>
     </row>
     <row r="43">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>234</v>
+        <v>800</v>
       </c>
       <c r="C43" t="inlineStr"/>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>220</v>
+        <v>796</v>
       </c>
     </row>
     <row r="45">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>224</v>
+        <v>754</v>
       </c>
       <c r="C45" t="inlineStr"/>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>232</v>
+        <v>786</v>
       </c>
     </row>
     <row r="47">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>239</v>
+        <v>765</v>
       </c>
       <c r="C47" t="inlineStr"/>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>226</v>
+        <v>692</v>
       </c>
       <c r="C48" t="inlineStr"/>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>224</v>
+        <v>858</v>
       </c>
     </row>
     <row r="50">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>248</v>
+        <v>708</v>
       </c>
       <c r="C50" t="inlineStr"/>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>248</v>
+        <v>806</v>
       </c>
     </row>
     <row r="52">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>232</v>
+        <v>828</v>
       </c>
       <c r="C52" t="inlineStr"/>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>222</v>
+        <v>812</v>
       </c>
     </row>
     <row r="54">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>232</v>
+        <v>862</v>
       </c>
       <c r="C54" t="inlineStr"/>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>242</v>
+        <v>840</v>
       </c>
     </row>
     <row r="56">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>288</v>
+        <v>744</v>
       </c>
       <c r="C56" t="inlineStr"/>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>212</v>
+        <v>788</v>
       </c>
     </row>
     <row r="58">
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>257</v>
+        <v>689</v>
       </c>
       <c r="C58" t="inlineStr"/>
     </row>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>276</v>
+        <v>702</v>
       </c>
       <c r="C59" t="inlineStr"/>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>160</v>
+        <v>754</v>
       </c>
     </row>
     <row r="61">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>242</v>
+        <v>672</v>
       </c>
       <c r="C61" t="inlineStr"/>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>210</v>
+        <v>952</v>
       </c>
     </row>
     <row r="63">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>216</v>
+        <v>830</v>
       </c>
       <c r="C63" t="inlineStr"/>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>208</v>
+        <v>758</v>
       </c>
     </row>
     <row r="65">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>292</v>
+        <v>830</v>
       </c>
       <c r="C65" t="inlineStr"/>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>214</v>
+        <v>740</v>
       </c>
     </row>
     <row r="67">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>230</v>
+        <v>814</v>
       </c>
       <c r="C67" t="inlineStr"/>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>206</v>
+        <v>708</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>224</v>
+        <v>508</v>
       </c>
     </row>
     <row r="70">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>312</v>
+        <v>734</v>
       </c>
       <c r="C70" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>214</v>
+        <v>882</v>
       </c>
     </row>
     <row r="72">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>230</v>
+        <v>740</v>
       </c>
       <c r="C72" t="inlineStr"/>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>212</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>230</v>
+        <v>826</v>
       </c>
       <c r="C74" t="inlineStr"/>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>232</v>
+        <v>806</v>
       </c>
     </row>
     <row r="76">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>236</v>
+        <v>774</v>
       </c>
       <c r="C76" t="inlineStr"/>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>212</v>
+        <v>800</v>
       </c>
     </row>
     <row r="78">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>254</v>
+        <v>814</v>
       </c>
       <c r="C78" t="inlineStr"/>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>214</v>
+        <v>802</v>
       </c>
     </row>
     <row r="80">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>244</v>
+        <v>732</v>
       </c>
       <c r="C80" t="inlineStr"/>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>276</v>
+        <v>727</v>
       </c>
     </row>
     <row r="82">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>228</v>
+        <v>762</v>
       </c>
       <c r="C82" t="inlineStr"/>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>214</v>
+        <v>902</v>
       </c>
     </row>
     <row r="84">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>270</v>
+        <v>768</v>
       </c>
       <c r="C84" t="inlineStr"/>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>214</v>
+        <v>782</v>
       </c>
     </row>
     <row r="86">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>234</v>
+        <v>696</v>
       </c>
       <c r="C86" t="inlineStr"/>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>212</v>
+        <v>854</v>
       </c>
     </row>
     <row r="88">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>264</v>
+        <v>816</v>
       </c>
       <c r="C88" t="inlineStr"/>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>214</v>
+        <v>798</v>
       </c>
     </row>
     <row r="90">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>288</v>
+        <v>715</v>
       </c>
       <c r="C90" t="inlineStr"/>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>220</v>
+        <v>758</v>
       </c>
     </row>
     <row r="92">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>216</v>
+        <v>794</v>
       </c>
       <c r="C92" t="inlineStr"/>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>234</v>
+        <v>848</v>
       </c>
     </row>
     <row r="94">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>220</v>
+        <v>744</v>
       </c>
     </row>
     <row r="95">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>229</v>
+        <v>804</v>
       </c>
       <c r="C95" t="inlineStr"/>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>216</v>
+        <v>796</v>
       </c>
     </row>
     <row r="97">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>234</v>
+        <v>763</v>
       </c>
       <c r="C97" t="inlineStr"/>
     </row>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>250</v>
+        <v>883</v>
       </c>
       <c r="C98" t="inlineStr"/>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>250</v>
+        <v>772</v>
       </c>
     </row>
     <row r="100">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>225</v>
+        <v>846</v>
       </c>
       <c r="C100" t="inlineStr"/>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>293</v>
+        <v>722</v>
       </c>
     </row>
     <row r="102">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>275</v>
+        <v>915</v>
       </c>
       <c r="C102" t="inlineStr"/>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>290</v>
+        <v>758</v>
       </c>
     </row>
     <row r="104">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>238</v>
+        <v>763</v>
       </c>
       <c r="C104" t="inlineStr"/>
     </row>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>235</v>
+        <v>883</v>
       </c>
       <c r="C105" t="inlineStr"/>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>211</v>
+        <v>730</v>
       </c>
     </row>
     <row r="107">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>215</v>
+        <v>834</v>
       </c>
     </row>
     <row r="108">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>256</v>
+        <v>738</v>
       </c>
       <c r="C108" t="inlineStr"/>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>247</v>
+        <v>735</v>
       </c>
     </row>
     <row r="110">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>224</v>
+        <v>777</v>
       </c>
       <c r="C110" t="inlineStr"/>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>209</v>
+        <v>774</v>
       </c>
     </row>
     <row r="112">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>237</v>
+        <v>821</v>
       </c>
       <c r="C112" t="inlineStr"/>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>207</v>
+        <v>755</v>
       </c>
     </row>
     <row r="114">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>236</v>
+        <v>1019</v>
       </c>
       <c r="C114" t="inlineStr"/>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>205</v>
+        <v>809</v>
       </c>
     </row>
     <row r="116">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>223</v>
+        <v>780</v>
       </c>
       <c r="C116" t="inlineStr"/>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>215</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="118">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>339</v>
+        <v>703</v>
       </c>
       <c r="C118" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>222</v>
+        <v>767</v>
       </c>
     </row>
     <row r="120">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>233</v>
+        <v>806</v>
       </c>
       <c r="C120" t="inlineStr"/>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>249</v>
+        <v>810</v>
       </c>
     </row>
     <row r="122">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>303</v>
+        <v>735</v>
       </c>
       <c r="C122" t="inlineStr"/>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>214</v>
+        <v>859</v>
       </c>
     </row>
     <row r="124">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>367</v>
+        <v>743</v>
       </c>
       <c r="C124" t="inlineStr"/>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>271</v>
+        <v>688</v>
       </c>
     </row>
     <row r="126">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>275</v>
+        <v>880</v>
       </c>
       <c r="C126" t="inlineStr"/>
     </row>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>347</v>
+        <v>859</v>
       </c>
       <c r="C127" t="inlineStr"/>
     </row>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>334</v>
+        <v>685</v>
       </c>
       <c r="C128" t="inlineStr"/>
     </row>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>331</v>
+        <v>765</v>
       </c>
       <c r="C129" t="inlineStr"/>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>214</v>
+        <v>834</v>
       </c>
     </row>
     <row r="131">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>298</v>
+        <v>749</v>
       </c>
       <c r="C131" t="inlineStr"/>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>234</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>145</v>
+        <v>819</v>
       </c>
       <c r="C133" t="inlineStr"/>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>216</v>
+        <v>857</v>
       </c>
     </row>
     <row r="135">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>328</v>
+        <v>689</v>
       </c>
       <c r="C135" t="inlineStr"/>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>142</v>
+        <v>856</v>
       </c>
     </row>
     <row r="137">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>301</v>
+        <v>964</v>
       </c>
       <c r="C137" t="inlineStr"/>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>210</v>
+        <v>816</v>
       </c>
     </row>
     <row r="139">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>454</v>
+        <v>849</v>
       </c>
       <c r="C139" t="inlineStr"/>
     </row>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>306</v>
+        <v>767</v>
       </c>
       <c r="C140" t="inlineStr"/>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>207</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
